--- a/three_gate/analysis/TX_weekly.xlsx
+++ b/three_gate/analysis/TX_weekly.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X10"/>
+  <dimension ref="A1:X15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -643,68 +643,82 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>43060</v>
+        <v>47460</v>
       </c>
       <c r="C2" t="n">
-        <v>44005</v>
+        <v>49240</v>
       </c>
       <c r="D2" t="n">
-        <v>41912</v>
+        <v>44264</v>
       </c>
       <c r="E2" t="n">
-        <v>42604</v>
+        <v>45805</v>
       </c>
       <c r="F2" t="n">
-        <v>-523</v>
+        <v>-231</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0121</v>
+        <v>-0.005</v>
       </c>
       <c r="H2" t="n">
-        <v>2093</v>
+        <v>4976</v>
       </c>
       <c r="I2" t="n">
-        <v>39710</v>
+        <v>43074</v>
       </c>
       <c r="J2" t="n">
-        <v>40058</v>
+        <v>44276</v>
       </c>
       <c r="K2" t="n">
-        <v>41762</v>
+        <v>45110</v>
       </c>
       <c r="L2" t="n">
-        <v>43466</v>
+        <v>45944</v>
       </c>
       <c r="M2" t="n">
-        <v>44492</v>
+        <v>46962</v>
       </c>
       <c r="N2" t="n">
-        <v>45518</v>
+        <v>47980</v>
       </c>
       <c r="O2" t="n">
-        <v>47900</v>
+        <v>48630</v>
       </c>
       <c r="P2" s="6" t="inlineStr"/>
-      <c r="Q2" s="6" t="inlineStr"/>
+      <c r="Q2" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="R2" s="7" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S2" s="8" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T2" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U2" s="6" t="inlineStr"/>
-      <c r="V2" s="6" t="inlineStr"/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T2" s="9" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="9" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="9" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="W2" s="10" t="inlineStr">
         <is>
           <t>多方</t>
@@ -712,145 +726,161 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>42800</v>
+        <v>44799</v>
       </c>
       <c r="C3" t="n">
-        <v>44480</v>
+        <v>47695</v>
       </c>
       <c r="D3" t="n">
-        <v>42120</v>
+        <v>44135</v>
       </c>
       <c r="E3" t="n">
-        <v>43814</v>
+        <v>45668</v>
       </c>
       <c r="F3" t="n">
-        <v>1210</v>
+        <v>-137</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0284</v>
+        <v>-0.003</v>
       </c>
       <c r="H3" t="n">
-        <v>2360</v>
+        <v>3560</v>
       </c>
       <c r="I3" t="n">
-        <v>39819</v>
+        <v>39288</v>
       </c>
       <c r="J3" t="n">
-        <v>40333.75</v>
+        <v>40355.5</v>
       </c>
       <c r="K3" t="n">
-        <v>41557.5</v>
+        <v>43317</v>
       </c>
       <c r="L3" t="n">
-        <v>42781.25</v>
+        <v>46278.5</v>
       </c>
       <c r="M3" t="n">
-        <v>43650.5</v>
+        <v>48293</v>
       </c>
       <c r="N3" t="n">
-        <v>44519.75</v>
+        <v>50307.5</v>
       </c>
       <c r="O3" t="n">
-        <v>46098</v>
+        <v>54216</v>
       </c>
       <c r="P3" s="6" t="inlineStr"/>
-      <c r="Q3" s="6" t="inlineStr"/>
+      <c r="Q3" s="7" t="n">
+        <v/>
+      </c>
       <c r="R3" s="7" t="n">
         <v/>
       </c>
-      <c r="S3" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="9" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U3" s="6" t="inlineStr"/>
-      <c r="V3" s="6" t="inlineStr"/>
+      <c r="S3" s="8" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T3" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U3" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V3" s="9" t="n">
+        <v/>
+      </c>
       <c r="W3" s="10" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>43900</v>
+        <v>47280</v>
       </c>
       <c r="C4" t="n">
-        <v>44380</v>
+        <v>47547</v>
       </c>
       <c r="D4" t="n">
-        <v>42700</v>
+        <v>44575</v>
       </c>
       <c r="E4" t="n">
-        <v>43727</v>
+        <v>45727</v>
       </c>
       <c r="F4" t="n">
-        <v>-87</v>
+        <v>59</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.0013</v>
       </c>
       <c r="H4" t="n">
-        <v>1680</v>
+        <v>2972</v>
       </c>
       <c r="I4" t="n">
-        <v>39760</v>
+        <v>40575</v>
       </c>
       <c r="J4" t="n">
-        <v>41711</v>
+        <v>41984.5</v>
       </c>
       <c r="K4" t="n">
-        <v>42634</v>
+        <v>43888</v>
       </c>
       <c r="L4" t="n">
-        <v>43557</v>
+        <v>45791.5</v>
       </c>
       <c r="M4" t="n">
-        <v>44994</v>
+        <v>47448</v>
       </c>
       <c r="N4" t="n">
-        <v>46431</v>
+        <v>49104.5</v>
       </c>
       <c r="O4" t="n">
-        <v>46840</v>
+        <v>51255</v>
       </c>
       <c r="P4" s="6" t="inlineStr"/>
-      <c r="Q4" s="6" t="inlineStr"/>
+      <c r="Q4" s="7" t="n">
+        <v/>
+      </c>
       <c r="R4" s="7" t="n">
         <v/>
       </c>
-      <c r="S4" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T4" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U4" s="6" t="inlineStr"/>
-      <c r="V4" s="6" t="inlineStr"/>
+      <c r="S4" s="8" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T4" s="9" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U4" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V4" s="9" t="n">
+        <v/>
+      </c>
       <c r="W4" s="10" t="inlineStr">
         <is>
           <t>多方</t>
@@ -858,204 +888,230 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>43800</v>
+        <v>46222</v>
       </c>
       <c r="C5" t="n">
-        <v>44975</v>
+        <v>46495</v>
       </c>
       <c r="D5" t="n">
-        <v>43000</v>
+        <v>42527</v>
       </c>
       <c r="E5" t="n">
-        <v>44297</v>
+        <v>44715</v>
       </c>
       <c r="F5" t="n">
-        <v>570</v>
+        <v>-1012</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.013</v>
+        <v>-0.0221</v>
       </c>
       <c r="H5" t="n">
-        <v>1975</v>
+        <v>3968</v>
       </c>
       <c r="I5" t="n">
-        <v>41020</v>
+        <v>41603</v>
       </c>
       <c r="J5" t="n">
-        <v>42140.5</v>
+        <v>42588</v>
       </c>
       <c r="K5" t="n">
-        <v>42887</v>
+        <v>44241</v>
       </c>
       <c r="L5" t="n">
-        <v>43633.5</v>
+        <v>45894</v>
       </c>
       <c r="M5" t="n">
-        <v>44567</v>
+        <v>47213</v>
       </c>
       <c r="N5" t="n">
-        <v>45500.5</v>
+        <v>48532</v>
       </c>
       <c r="O5" t="n">
-        <v>46060</v>
+        <v>50519</v>
       </c>
       <c r="P5" s="6" t="inlineStr"/>
-      <c r="Q5" s="6" t="inlineStr"/>
-      <c r="R5" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S5" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="9" t="inlineStr">
+      <c r="Q5" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R5" s="7" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U5" s="6" t="inlineStr"/>
-      <c r="V5" s="6" t="inlineStr"/>
+      <c r="S5" s="8" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T5" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U5" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V5" s="9" t="n">
+        <v/>
+      </c>
       <c r="W5" s="10" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>44380</v>
+        <v>43500</v>
       </c>
       <c r="C6" t="n">
-        <v>46113</v>
+        <v>45364</v>
       </c>
       <c r="D6" t="n">
-        <v>44000</v>
+        <v>42173</v>
       </c>
       <c r="E6" t="n">
-        <v>45812</v>
+        <v>44391</v>
       </c>
       <c r="F6" t="n">
-        <v>1515</v>
+        <v>-324</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0342</v>
+        <v>-0.0072</v>
       </c>
       <c r="H6" t="n">
-        <v>2113</v>
+        <v>3191</v>
       </c>
       <c r="I6" t="n">
-        <v>41025</v>
+        <v>38559</v>
       </c>
       <c r="J6" t="n">
-        <v>42476.75</v>
+        <v>40849</v>
       </c>
       <c r="K6" t="n">
-        <v>43309.5</v>
+        <v>42731</v>
       </c>
       <c r="L6" t="n">
-        <v>44142.25</v>
+        <v>44613</v>
       </c>
       <c r="M6" t="n">
-        <v>45284.5</v>
+        <v>46699</v>
       </c>
       <c r="N6" t="n">
-        <v>46426.75</v>
+        <v>48785</v>
       </c>
       <c r="O6" t="n">
-        <v>46950</v>
+        <v>50463</v>
       </c>
       <c r="P6" s="6" t="inlineStr"/>
-      <c r="Q6" s="6" t="inlineStr"/>
-      <c r="R6" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="9" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U6" s="6" t="inlineStr"/>
-      <c r="V6" s="6" t="inlineStr"/>
+      <c r="Q6" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S6" s="8" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T6" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U6" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V6" s="9" t="n">
+        <v/>
+      </c>
       <c r="W6" s="10" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>45852</v>
+        <v>43888</v>
       </c>
       <c r="C7" t="n">
-        <v>46297</v>
+        <v>44306</v>
       </c>
       <c r="D7" t="n">
-        <v>44208</v>
+        <v>39442</v>
       </c>
       <c r="E7" t="n">
-        <v>45138</v>
+        <v>41859</v>
       </c>
       <c r="F7" t="n">
-        <v>-674</v>
+        <v>-2532</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0147</v>
+        <v>-0.057</v>
       </c>
       <c r="H7" t="n">
-        <v>2089</v>
+        <v>4864</v>
       </c>
       <c r="I7" t="n">
-        <v>41887</v>
+        <v>38982</v>
       </c>
       <c r="J7" t="n">
-        <v>44076.75</v>
+        <v>41511.25</v>
       </c>
       <c r="K7" t="n">
-        <v>44755.5</v>
+        <v>42795.5</v>
       </c>
       <c r="L7" t="n">
-        <v>45434.25</v>
+        <v>44079.75</v>
       </c>
       <c r="M7" t="n">
-        <v>46868.5</v>
+        <v>45986.5</v>
       </c>
       <c r="N7" t="n">
-        <v>48302.75</v>
+        <v>47893.25</v>
       </c>
       <c r="O7" t="n">
-        <v>48226</v>
+        <v>48555</v>
       </c>
       <c r="P7" s="6" t="inlineStr"/>
-      <c r="Q7" s="6" t="inlineStr"/>
+      <c r="Q7" s="7" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
       <c r="R7" s="7" t="inlineStr">
         <is>
           <t>✓</t>
@@ -1063,14 +1119,18 @@
       </c>
       <c r="S7" s="8" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T7" s="9" t="n">
         <v/>
       </c>
-      <c r="U7" s="6" t="inlineStr"/>
-      <c r="V7" s="6" t="inlineStr"/>
+      <c r="U7" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V7" s="9" t="n">
+        <v/>
+      </c>
       <c r="W7" s="10" t="inlineStr">
         <is>
           <t>多方</t>
@@ -1078,60 +1138,62 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>45220</v>
+        <v>43186</v>
       </c>
       <c r="C8" t="n">
-        <v>46580</v>
+        <v>44923</v>
       </c>
       <c r="D8" t="n">
-        <v>44146</v>
+        <v>42086</v>
       </c>
       <c r="E8" t="n">
-        <v>46357</v>
+        <v>44543</v>
       </c>
       <c r="F8" t="n">
-        <v>1219</v>
+        <v>2684</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.027</v>
+        <v>0.0641</v>
       </c>
       <c r="H8" t="n">
-        <v>2434</v>
+        <v>2837</v>
       </c>
       <c r="I8" t="n">
-        <v>42119</v>
+        <v>34578</v>
       </c>
       <c r="J8" t="n">
-        <v>42991.75</v>
+        <v>36987.5</v>
       </c>
       <c r="K8" t="n">
-        <v>44093.5</v>
+        <v>39427</v>
       </c>
       <c r="L8" t="n">
-        <v>45195.25</v>
+        <v>41866.5</v>
       </c>
       <c r="M8" t="n">
-        <v>46182.5</v>
+        <v>44291</v>
       </c>
       <c r="N8" t="n">
-        <v>47169.75</v>
+        <v>46715.5</v>
       </c>
       <c r="O8" t="n">
-        <v>48386</v>
+        <v>49170</v>
       </c>
       <c r="P8" s="6" t="inlineStr"/>
-      <c r="Q8" s="6" t="inlineStr"/>
+      <c r="Q8" s="7" t="n">
+        <v/>
+      </c>
       <c r="R8" s="7" t="n">
         <v/>
       </c>
@@ -1145,69 +1207,71 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U8" s="6" t="inlineStr"/>
-      <c r="V8" s="6" t="inlineStr"/>
+      <c r="U8" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V8" s="9" t="n">
+        <v/>
+      </c>
       <c r="W8" s="10" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>45951</v>
+        <v>44985</v>
       </c>
       <c r="C9" t="n">
-        <v>47343</v>
+        <v>46574</v>
       </c>
       <c r="D9" t="n">
-        <v>45415</v>
+        <v>44362</v>
       </c>
       <c r="E9" t="n">
-        <v>47182</v>
+        <v>46389</v>
       </c>
       <c r="F9" t="n">
-        <v>825</v>
+        <v>1846</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0178</v>
+        <v>0.0414</v>
       </c>
       <c r="H9" t="n">
-        <v>1928</v>
+        <v>2212</v>
       </c>
       <c r="I9" t="n">
-        <v>41712</v>
+        <v>39249</v>
       </c>
       <c r="J9" t="n">
-        <v>44420</v>
+        <v>42225.25</v>
       </c>
       <c r="K9" t="n">
-        <v>45140</v>
+        <v>43124.5</v>
       </c>
       <c r="L9" t="n">
-        <v>45860</v>
+        <v>44023.75</v>
       </c>
       <c r="M9" t="n">
-        <v>47574</v>
+        <v>45961.5</v>
       </c>
       <c r="N9" t="n">
-        <v>49288</v>
+        <v>47899.25</v>
       </c>
       <c r="O9" t="n">
-        <v>49014</v>
+        <v>47760</v>
       </c>
       <c r="P9" s="6" t="inlineStr"/>
-      <c r="Q9" s="6" t="inlineStr"/>
+      <c r="Q9" s="7" t="n">
+        <v/>
+      </c>
       <c r="R9" s="7" t="n">
         <v/>
       </c>
@@ -1221,8 +1285,12 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U9" s="6" t="inlineStr"/>
-      <c r="V9" s="6" t="inlineStr"/>
+      <c r="U9" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V9" s="9" t="n">
+        <v/>
+      </c>
       <c r="W9" s="10" t="inlineStr">
         <is>
           <t>多方</t>
@@ -1231,31 +1299,439 @@
       <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>45850</v>
+      </c>
+      <c r="C10" t="n">
+        <v>46297</v>
+      </c>
+      <c r="D10" t="n">
+        <v>44208</v>
+      </c>
+      <c r="E10" t="n">
+        <v>44804</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-1585</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>-0.0342</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2089</v>
+      </c>
+      <c r="I10" t="n">
+        <v>42150</v>
+      </c>
+      <c r="J10" t="n">
+        <v>44637.5</v>
+      </c>
+      <c r="K10" t="n">
+        <v>45283</v>
+      </c>
+      <c r="L10" t="n">
+        <v>45928.5</v>
+      </c>
+      <c r="M10" t="n">
+        <v>47495</v>
+      </c>
+      <c r="N10" t="n">
+        <v>49061.5</v>
+      </c>
+      <c r="O10" t="n">
+        <v>48786</v>
+      </c>
+      <c r="P10" s="6" t="inlineStr"/>
+      <c r="Q10" s="7" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R10" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S10" s="8" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T10" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U10" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V10" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W10" s="10" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>45032</v>
+      </c>
+      <c r="C11" t="n">
+        <v>46580</v>
+      </c>
+      <c r="D11" t="n">
+        <v>44146</v>
+      </c>
+      <c r="E11" t="n">
+        <v>46388</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1584</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0.0354</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2434</v>
+      </c>
+      <c r="I11" t="n">
+        <v>42119</v>
+      </c>
+      <c r="J11" t="n">
+        <v>42490.75</v>
+      </c>
+      <c r="K11" t="n">
+        <v>43759.5</v>
+      </c>
+      <c r="L11" t="n">
+        <v>45028.25</v>
+      </c>
+      <c r="M11" t="n">
+        <v>45848.5</v>
+      </c>
+      <c r="N11" t="n">
+        <v>46668.75</v>
+      </c>
+      <c r="O11" t="n">
+        <v>48386</v>
+      </c>
+      <c r="P11" s="6" t="inlineStr"/>
+      <c r="Q11" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R11" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="9" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U11" s="9" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V11" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W11" s="10" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>45800</v>
+      </c>
+      <c r="C12" t="n">
+        <v>47343</v>
+      </c>
+      <c r="D12" t="n">
+        <v>45415</v>
+      </c>
+      <c r="E12" t="n">
+        <v>46487</v>
+      </c>
+      <c r="F12" t="n">
+        <v>99</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1928</v>
+      </c>
+      <c r="I12" t="n">
+        <v>41712</v>
+      </c>
+      <c r="J12" t="n">
+        <v>44466.5</v>
+      </c>
+      <c r="K12" t="n">
+        <v>45171</v>
+      </c>
+      <c r="L12" t="n">
+        <v>45875.5</v>
+      </c>
+      <c r="M12" t="n">
+        <v>47605</v>
+      </c>
+      <c r="N12" t="n">
+        <v>49334.5</v>
+      </c>
+      <c r="O12" t="n">
+        <v>49014</v>
+      </c>
+      <c r="P12" s="6" t="inlineStr"/>
+      <c r="Q12" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T12" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U12" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V12" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W12" s="10" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>47280</v>
+      </c>
+      <c r="C13" t="n">
+        <v>47593</v>
+      </c>
+      <c r="D13" t="n">
+        <v>45780</v>
+      </c>
+      <c r="E13" t="n">
+        <v>46072</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-415</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>-0.0089</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1813</v>
+      </c>
+      <c r="I13" t="n">
+        <v>43487</v>
+      </c>
+      <c r="J13" t="n">
+        <v>44613</v>
+      </c>
+      <c r="K13" t="n">
+        <v>45523</v>
+      </c>
+      <c r="L13" t="n">
+        <v>46433</v>
+      </c>
+      <c r="M13" t="n">
+        <v>47451</v>
+      </c>
+      <c r="N13" t="n">
+        <v>48469</v>
+      </c>
+      <c r="O13" t="n">
+        <v>49271</v>
+      </c>
+      <c r="P13" s="6" t="inlineStr"/>
+      <c r="Q13" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="8" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T13" s="9" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U13" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V13" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W13" s="10" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>45589</v>
+      </c>
+      <c r="C14" t="n">
+        <v>46663</v>
+      </c>
+      <c r="D14" t="n">
+        <v>45302</v>
+      </c>
+      <c r="E14" t="n">
+        <v>45529</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-543</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>-0.0118</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1361</v>
+      </c>
+      <c r="I14" t="n">
+        <v>43967</v>
+      </c>
+      <c r="J14" t="n">
+        <v>43951.75</v>
+      </c>
+      <c r="K14" t="n">
+        <v>45165.5</v>
+      </c>
+      <c r="L14" t="n">
+        <v>46379.25</v>
+      </c>
+      <c r="M14" t="n">
+        <v>46978.5</v>
+      </c>
+      <c r="N14" t="n">
+        <v>47577.75</v>
+      </c>
+      <c r="O14" t="n">
+        <v>49406</v>
+      </c>
+      <c r="P14" s="6" t="inlineStr"/>
+      <c r="Q14" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="7" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S14" s="8" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T14" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U14" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V14" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W14" s="10" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>下週預測</t>
         </is>
       </c>
-      <c r="I10" s="13" t="n">
-        <v>43487</v>
-      </c>
-      <c r="J10" s="13" t="n">
-        <v>45655.5</v>
-      </c>
-      <c r="K10" s="13" t="n">
-        <v>46218</v>
-      </c>
-      <c r="L10" s="13" t="n">
-        <v>46780.5</v>
-      </c>
-      <c r="M10" s="13" t="n">
-        <v>48146</v>
-      </c>
-      <c r="N10" s="13" t="n">
-        <v>49511.5</v>
-      </c>
-      <c r="O10" s="13" t="n">
-        <v>49271</v>
+      <c r="I15" s="13" t="n">
+        <v>43941</v>
+      </c>
+      <c r="J15" s="13" t="n">
+        <v>43941.25</v>
+      </c>
+      <c r="K15" s="13" t="n">
+        <v>44848.5</v>
+      </c>
+      <c r="L15" s="13" t="n">
+        <v>45755.75</v>
+      </c>
+      <c r="M15" s="13" t="n">
+        <v>46209.5</v>
+      </c>
+      <c r="N15" s="13" t="n">
+        <v>46663.25</v>
+      </c>
+      <c r="O15" s="13" t="n">
+        <v>48024</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/TX_weekly.xlsx
+++ b/three_gate/analysis/TX_weekly.xlsx
@@ -1640,13 +1640,13 @@
         <v>45302</v>
       </c>
       <c r="E14" t="n">
-        <v>45529</v>
+        <v>46382</v>
       </c>
       <c r="F14" t="n">
-        <v>-543</v>
+        <v>310</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0118</v>
+        <v>0.0067</v>
       </c>
       <c r="H14" t="n">
         <v>1361</v>
@@ -1676,14 +1676,12 @@
       <c r="Q14" s="7" t="n">
         <v/>
       </c>
-      <c r="R14" s="7" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S14" s="8" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R14" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T14" s="9" t="n">
@@ -1702,7 +1700,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
@@ -1716,19 +1714,19 @@
         <v>43941</v>
       </c>
       <c r="J15" s="13" t="n">
-        <v>43941.25</v>
+        <v>45220.75</v>
       </c>
       <c r="K15" s="13" t="n">
-        <v>44848.5</v>
+        <v>45701.5</v>
       </c>
       <c r="L15" s="13" t="n">
-        <v>45755.75</v>
+        <v>46182.25</v>
       </c>
       <c r="M15" s="13" t="n">
-        <v>46209.5</v>
+        <v>47062.5</v>
       </c>
       <c r="N15" s="13" t="n">
-        <v>46663.25</v>
+        <v>47942.75</v>
       </c>
       <c r="O15" s="13" t="n">
         <v>48024</v>

--- a/three_gate/analysis/TX_weekly.xlsx
+++ b/three_gate/analysis/TX_weekly.xlsx
@@ -1634,22 +1634,22 @@
         <v>45589</v>
       </c>
       <c r="C14" t="n">
-        <v>46663</v>
+        <v>47205</v>
       </c>
       <c r="D14" t="n">
         <v>45302</v>
       </c>
       <c r="E14" t="n">
-        <v>46382</v>
+        <v>47160</v>
       </c>
       <c r="F14" t="n">
-        <v>310</v>
+        <v>1088</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0067</v>
+        <v>0.0236</v>
       </c>
       <c r="H14" t="n">
-        <v>1361</v>
+        <v>1903</v>
       </c>
       <c r="I14" t="n">
         <v>43967</v>
@@ -1681,11 +1681,13 @@
       </c>
       <c r="S14" s="11" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T14" s="9" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="9" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U14" s="9" t="n">
         <v/>
@@ -1711,25 +1713,25 @@
         </is>
       </c>
       <c r="I15" s="13" t="n">
-        <v>43941</v>
+        <v>43399</v>
       </c>
       <c r="J15" s="13" t="n">
-        <v>45220.75</v>
+        <v>45710.25</v>
       </c>
       <c r="K15" s="13" t="n">
-        <v>45701.5</v>
+        <v>46208.5</v>
       </c>
       <c r="L15" s="13" t="n">
-        <v>46182.25</v>
+        <v>46706.75</v>
       </c>
       <c r="M15" s="13" t="n">
-        <v>47062.5</v>
+        <v>48111.5</v>
       </c>
       <c r="N15" s="13" t="n">
-        <v>47942.75</v>
+        <v>49516.25</v>
       </c>
       <c r="O15" s="13" t="n">
-        <v>48024</v>
+        <v>49108</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/TX_weekly.xlsx
+++ b/three_gate/analysis/TX_weekly.xlsx
@@ -46,7 +46,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -73,11 +73,6 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -91,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -122,8 +117,6 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -489,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X15"/>
+  <dimension ref="A1:X14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1706,34 +1699,6 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>下週預測</t>
-        </is>
-      </c>
-      <c r="I15" s="13" t="n">
-        <v>43399</v>
-      </c>
-      <c r="J15" s="13" t="n">
-        <v>45710.25</v>
-      </c>
-      <c r="K15" s="13" t="n">
-        <v>46208.5</v>
-      </c>
-      <c r="L15" s="13" t="n">
-        <v>46706.75</v>
-      </c>
-      <c r="M15" s="13" t="n">
-        <v>48111.5</v>
-      </c>
-      <c r="N15" s="13" t="n">
-        <v>49516.25</v>
-      </c>
-      <c r="O15" s="13" t="n">
-        <v>49108</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/TX_weekly.xlsx
+++ b/three_gate/analysis/TX_weekly.xlsx
@@ -1627,22 +1627,22 @@
         <v>45589</v>
       </c>
       <c r="C14" t="n">
-        <v>47205</v>
+        <v>47464</v>
       </c>
       <c r="D14" t="n">
         <v>45302</v>
       </c>
       <c r="E14" t="n">
-        <v>47160</v>
+        <v>47418</v>
       </c>
       <c r="F14" t="n">
-        <v>1088</v>
+        <v>1346</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0236</v>
+        <v>0.0292</v>
       </c>
       <c r="H14" t="n">
-        <v>1903</v>
+        <v>2162</v>
       </c>
       <c r="I14" t="n">
         <v>43967</v>
@@ -1679,11 +1679,13 @@
       </c>
       <c r="T14" s="9" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U14" s="9" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U14" s="9" t="n">
-        <v/>
       </c>
       <c r="V14" s="9" t="n">
         <v/>

--- a/three_gate/analysis/TX_weekly.xlsx
+++ b/three_gate/analysis/TX_weekly.xlsx
@@ -482,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X14"/>
+  <dimension ref="A1:X15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1701,6 +1701,84 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>47607</v>
+      </c>
+      <c r="C15" t="n">
+        <v>48805</v>
+      </c>
+      <c r="D15" t="n">
+        <v>47496</v>
+      </c>
+      <c r="E15" t="n">
+        <v>48781</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1363</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>0.0287</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1309</v>
+      </c>
+      <c r="I15" t="n">
+        <v>43140</v>
+      </c>
+      <c r="J15" t="n">
+        <v>45773.5</v>
+      </c>
+      <c r="K15" t="n">
+        <v>46337</v>
+      </c>
+      <c r="L15" t="n">
+        <v>46900.5</v>
+      </c>
+      <c r="M15" t="n">
+        <v>48499</v>
+      </c>
+      <c r="N15" t="n">
+        <v>50097.5</v>
+      </c>
+      <c r="O15" t="n">
+        <v>49626</v>
+      </c>
+      <c r="P15" s="6" t="inlineStr"/>
+      <c r="Q15" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="9" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U15" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V15" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W15" s="10" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/TX_weekly.xlsx
+++ b/three_gate/analysis/TX_weekly.xlsx
@@ -1711,22 +1711,22 @@
         <v>47607</v>
       </c>
       <c r="C15" t="n">
-        <v>48805</v>
+        <v>48946</v>
       </c>
       <c r="D15" t="n">
         <v>47496</v>
       </c>
       <c r="E15" t="n">
-        <v>48781</v>
+        <v>48243</v>
       </c>
       <c r="F15" t="n">
-        <v>1363</v>
+        <v>825</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0287</v>
+        <v>0.0174</v>
       </c>
       <c r="H15" t="n">
-        <v>1309</v>
+        <v>1450</v>
       </c>
       <c r="I15" t="n">
         <v>43140</v>

--- a/three_gate/analysis/TX_weekly.xlsx
+++ b/three_gate/analysis/TX_weekly.xlsx
@@ -1717,13 +1717,13 @@
         <v>47496</v>
       </c>
       <c r="E15" t="n">
-        <v>48243</v>
+        <v>48497</v>
       </c>
       <c r="F15" t="n">
-        <v>825</v>
+        <v>1079</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0174</v>
+        <v>0.0228</v>
       </c>
       <c r="H15" t="n">
         <v>1450</v>

--- a/three_gate/analysis/TX_weekly.xlsx
+++ b/three_gate/analysis/TX_weekly.xlsx
@@ -1717,13 +1717,13 @@
         <v>47496</v>
       </c>
       <c r="E15" t="n">
-        <v>48497</v>
+        <v>48336</v>
       </c>
       <c r="F15" t="n">
-        <v>1079</v>
+        <v>918</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0228</v>
+        <v>0.0194</v>
       </c>
       <c r="H15" t="n">
         <v>1450</v>

--- a/three_gate/analysis/TX_weekly.xlsx
+++ b/three_gate/analysis/TX_weekly.xlsx
@@ -1717,13 +1717,13 @@
         <v>47496</v>
       </c>
       <c r="E15" t="n">
-        <v>48336</v>
+        <v>47909</v>
       </c>
       <c r="F15" t="n">
-        <v>918</v>
+        <v>491</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0194</v>
+        <v>0.0104</v>
       </c>
       <c r="H15" t="n">
         <v>1450</v>

--- a/three_gate/analysis/TX_weekly.xlsx
+++ b/three_gate/analysis/TX_weekly.xlsx
@@ -1717,13 +1717,13 @@
         <v>47496</v>
       </c>
       <c r="E15" t="n">
-        <v>47909</v>
+        <v>48123</v>
       </c>
       <c r="F15" t="n">
-        <v>491</v>
+        <v>705</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0104</v>
+        <v>0.0149</v>
       </c>
       <c r="H15" t="n">
         <v>1450</v>

--- a/three_gate/analysis/TX_weekly.xlsx
+++ b/three_gate/analysis/TX_weekly.xlsx
@@ -482,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X15"/>
+  <dimension ref="A1:X16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1779,6 +1779,86 @@
       </c>
       <c r="X15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>47915</v>
+      </c>
+      <c r="C16" t="n">
+        <v>48296</v>
+      </c>
+      <c r="D16" t="n">
+        <v>47769</v>
+      </c>
+      <c r="E16" t="n">
+        <v>47956</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-167</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>-0.0035</v>
+      </c>
+      <c r="H16" t="n">
+        <v>527</v>
+      </c>
+      <c r="I16" t="n">
+        <v>46046</v>
+      </c>
+      <c r="J16" t="n">
+        <v>46624</v>
+      </c>
+      <c r="K16" t="n">
+        <v>47398</v>
+      </c>
+      <c r="L16" t="n">
+        <v>48172</v>
+      </c>
+      <c r="M16" t="n">
+        <v>48848</v>
+      </c>
+      <c r="N16" t="n">
+        <v>49524</v>
+      </c>
+      <c r="O16" t="n">
+        <v>50396</v>
+      </c>
+      <c r="P16" s="6" t="inlineStr"/>
+      <c r="Q16" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="8" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T16" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U16" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V16" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W16" s="10" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/TX_weekly.xlsx
+++ b/three_gate/analysis/TX_weekly.xlsx
@@ -1789,22 +1789,22 @@
         <v>47915</v>
       </c>
       <c r="C16" t="n">
-        <v>48296</v>
+        <v>48619</v>
       </c>
       <c r="D16" t="n">
-        <v>47769</v>
+        <v>47630</v>
       </c>
       <c r="E16" t="n">
-        <v>47956</v>
+        <v>48479</v>
       </c>
       <c r="F16" t="n">
-        <v>-167</v>
+        <v>356</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0035</v>
+        <v>0.0074</v>
       </c>
       <c r="H16" t="n">
-        <v>527</v>
+        <v>989</v>
       </c>
       <c r="I16" t="n">
         <v>46046</v>
@@ -1834,9 +1834,9 @@
       <c r="R16" s="7" t="n">
         <v/>
       </c>
-      <c r="S16" s="8" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S16" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T16" s="9" t="n">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/TX_weekly.xlsx
+++ b/three_gate/analysis/TX_weekly.xlsx
@@ -1789,22 +1789,22 @@
         <v>47915</v>
       </c>
       <c r="C16" t="n">
-        <v>48619</v>
+        <v>48646</v>
       </c>
       <c r="D16" t="n">
         <v>47630</v>
       </c>
       <c r="E16" t="n">
-        <v>48479</v>
+        <v>48298</v>
       </c>
       <c r="F16" t="n">
-        <v>356</v>
+        <v>175</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0074</v>
+        <v>0.0036</v>
       </c>
       <c r="H16" t="n">
-        <v>989</v>
+        <v>1016</v>
       </c>
       <c r="I16" t="n">
         <v>46046</v>

--- a/three_gate/analysis/TX_weekly.xlsx
+++ b/three_gate/analysis/TX_weekly.xlsx
@@ -1789,22 +1789,22 @@
         <v>47915</v>
       </c>
       <c r="C16" t="n">
-        <v>48646</v>
+        <v>48719</v>
       </c>
       <c r="D16" t="n">
         <v>47630</v>
       </c>
       <c r="E16" t="n">
-        <v>48298</v>
+        <v>48475</v>
       </c>
       <c r="F16" t="n">
-        <v>175</v>
+        <v>352</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0036</v>
+        <v>0.0073</v>
       </c>
       <c r="H16" t="n">
-        <v>1016</v>
+        <v>1089</v>
       </c>
       <c r="I16" t="n">
         <v>46046</v>

--- a/three_gate/analysis/TX_weekly.xlsx
+++ b/three_gate/analysis/TX_weekly.xlsx
@@ -1789,22 +1789,22 @@
         <v>47915</v>
       </c>
       <c r="C16" t="n">
-        <v>48719</v>
+        <v>48802</v>
       </c>
       <c r="D16" t="n">
         <v>47630</v>
       </c>
       <c r="E16" t="n">
-        <v>48475</v>
+        <v>48671</v>
       </c>
       <c r="F16" t="n">
-        <v>352</v>
+        <v>548</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0073</v>
+        <v>0.0114</v>
       </c>
       <c r="H16" t="n">
-        <v>1089</v>
+        <v>1172</v>
       </c>
       <c r="I16" t="n">
         <v>46046</v>
@@ -1836,11 +1836,13 @@
       </c>
       <c r="S16" s="11" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T16" s="9" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="9" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U16" s="9" t="n">
         <v/>

--- a/three_gate/analysis/TX_weekly.xlsx
+++ b/three_gate/analysis/TX_weekly.xlsx
@@ -482,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X16"/>
+  <dimension ref="A1:X17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1861,6 +1861,88 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>49470</v>
+      </c>
+      <c r="C17" t="n">
+        <v>50247</v>
+      </c>
+      <c r="D17" t="n">
+        <v>49461</v>
+      </c>
+      <c r="E17" t="n">
+        <v>50118</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1447</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0.0297</v>
+      </c>
+      <c r="H17" t="n">
+        <v>786</v>
+      </c>
+      <c r="I17" t="n">
+        <v>46458</v>
+      </c>
+      <c r="J17" t="n">
+        <v>47726.5</v>
+      </c>
+      <c r="K17" t="n">
+        <v>48085</v>
+      </c>
+      <c r="L17" t="n">
+        <v>48443.5</v>
+      </c>
+      <c r="M17" t="n">
+        <v>49257</v>
+      </c>
+      <c r="N17" t="n">
+        <v>50070.5</v>
+      </c>
+      <c r="O17" t="n">
+        <v>49974</v>
+      </c>
+      <c r="P17" s="6" t="inlineStr"/>
+      <c r="Q17" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="9" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U17" s="9" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V17" s="9" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W17" s="10" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/TX_weekly.xlsx
+++ b/three_gate/analysis/TX_weekly.xlsx
@@ -1868,25 +1868,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>49470</v>
+        <v>49960</v>
       </c>
       <c r="C17" t="n">
-        <v>50247</v>
+        <v>50265</v>
       </c>
       <c r="D17" t="n">
-        <v>49461</v>
+        <v>49720</v>
       </c>
       <c r="E17" t="n">
-        <v>50118</v>
+        <v>50051</v>
       </c>
       <c r="F17" t="n">
-        <v>1447</v>
+        <v>1380</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0297</v>
+        <v>0.0284</v>
       </c>
       <c r="H17" t="n">
-        <v>786</v>
+        <v>545</v>
       </c>
       <c r="I17" t="n">
         <v>46458</v>

--- a/three_gate/analysis/TX_weekly.xlsx
+++ b/three_gate/analysis/TX_weekly.xlsx
@@ -1874,19 +1874,19 @@
         <v>50265</v>
       </c>
       <c r="D17" t="n">
-        <v>49720</v>
+        <v>49253</v>
       </c>
       <c r="E17" t="n">
-        <v>50051</v>
+        <v>49593</v>
       </c>
       <c r="F17" t="n">
-        <v>1380</v>
+        <v>922</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0284</v>
+        <v>0.0189</v>
       </c>
       <c r="H17" t="n">
-        <v>545</v>
+        <v>1012</v>
       </c>
       <c r="I17" t="n">
         <v>46458</v>
@@ -1923,12 +1923,12 @@
       </c>
       <c r="T17" s="9" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U17" s="9" t="inlineStr">
+        <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="U17" s="9" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="V17" s="9" t="inlineStr">

--- a/three_gate/analysis/TX_weekly.xlsx
+++ b/three_gate/analysis/TX_weekly.xlsx
@@ -1877,13 +1877,13 @@
         <v>49253</v>
       </c>
       <c r="E17" t="n">
-        <v>49593</v>
+        <v>49349</v>
       </c>
       <c r="F17" t="n">
-        <v>922</v>
+        <v>678</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0189</v>
+        <v>0.0139</v>
       </c>
       <c r="H17" t="n">
         <v>1012</v>

--- a/three_gate/analysis/TX_weekly.xlsx
+++ b/three_gate/analysis/TX_weekly.xlsx
@@ -482,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X17"/>
+  <dimension ref="A1:X18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1874,19 +1874,19 @@
         <v>50265</v>
       </c>
       <c r="D17" t="n">
-        <v>49253</v>
+        <v>48413</v>
       </c>
       <c r="E17" t="n">
-        <v>49349</v>
+        <v>48705</v>
       </c>
       <c r="F17" t="n">
-        <v>678</v>
+        <v>34</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0139</v>
+        <v>0.0007</v>
       </c>
       <c r="H17" t="n">
-        <v>1012</v>
+        <v>1852</v>
       </c>
       <c r="I17" t="n">
         <v>46458</v>
@@ -1918,12 +1918,12 @@
       </c>
       <c r="S17" s="11" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T17" s="9" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U17" s="9" t="inlineStr">
@@ -1942,6 +1942,86 @@
         </is>
       </c>
       <c r="X17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>49122</v>
+      </c>
+      <c r="C18" t="n">
+        <v>49226</v>
+      </c>
+      <c r="D18" t="n">
+        <v>48413</v>
+      </c>
+      <c r="E18" t="n">
+        <v>48705</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>813</v>
+      </c>
+      <c r="I18" t="n">
+        <v>46561</v>
+      </c>
+      <c r="J18" t="n">
+        <v>46536</v>
+      </c>
+      <c r="K18" t="n">
+        <v>47779</v>
+      </c>
+      <c r="L18" t="n">
+        <v>49022</v>
+      </c>
+      <c r="M18" t="n">
+        <v>49631</v>
+      </c>
+      <c r="N18" t="n">
+        <v>50240</v>
+      </c>
+      <c r="O18" t="n">
+        <v>52117</v>
+      </c>
+      <c r="P18" s="6" t="inlineStr"/>
+      <c r="Q18" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="8" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T18" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U18" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V18" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W18" s="10" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/TX_weekly.xlsx
+++ b/three_gate/analysis/TX_weekly.xlsx
@@ -1950,25 +1950,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>49122</v>
+        <v>48975</v>
       </c>
       <c r="C18" t="n">
-        <v>49226</v>
+        <v>49594</v>
       </c>
       <c r="D18" t="n">
-        <v>48413</v>
+        <v>48881</v>
       </c>
       <c r="E18" t="n">
-        <v>48705</v>
+        <v>48946</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>241</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0</v>
+        <v>0.0049</v>
       </c>
       <c r="H18" t="n">
-        <v>813</v>
+        <v>713</v>
       </c>
       <c r="I18" t="n">
         <v>46561</v>

--- a/three_gate/analysis/TX_weekly.xlsx
+++ b/three_gate/analysis/TX_weekly.xlsx
@@ -1956,19 +1956,19 @@
         <v>49594</v>
       </c>
       <c r="D18" t="n">
-        <v>48881</v>
+        <v>48240</v>
       </c>
       <c r="E18" t="n">
-        <v>48946</v>
+        <v>48755</v>
       </c>
       <c r="F18" t="n">
-        <v>241</v>
+        <v>50</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0049</v>
+        <v>0.001</v>
       </c>
       <c r="H18" t="n">
-        <v>713</v>
+        <v>1354</v>
       </c>
       <c r="I18" t="n">
         <v>46561</v>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/TX_weekly.xlsx
+++ b/three_gate/analysis/TX_weekly.xlsx
@@ -1956,19 +1956,19 @@
         <v>49594</v>
       </c>
       <c r="D18" t="n">
-        <v>48240</v>
+        <v>47850</v>
       </c>
       <c r="E18" t="n">
-        <v>48755</v>
+        <v>47945</v>
       </c>
       <c r="F18" t="n">
-        <v>50</v>
+        <v>-760</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.001</v>
+        <v>-0.0156</v>
       </c>
       <c r="H18" t="n">
-        <v>1354</v>
+        <v>1744</v>
       </c>
       <c r="I18" t="n">
         <v>46561</v>
@@ -1995,12 +1995,14 @@
       <c r="Q18" s="7" t="n">
         <v/>
       </c>
-      <c r="R18" s="7" t="n">
-        <v/>
+      <c r="R18" s="7" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S18" s="8" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T18" s="9" t="n">
@@ -2019,7 +2021,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/TX_weekly.xlsx
+++ b/three_gate/analysis/TX_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -101,9 +101,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -681,38 +678,40 @@
       <c r="O2" t="n">
         <v>48630</v>
       </c>
-      <c r="P2" s="6" t="inlineStr"/>
-      <c r="Q2" s="7" t="inlineStr">
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R2" s="7" t="inlineStr">
+      <c r="R2" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S2" s="8" t="inlineStr">
+      <c r="S2" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T2" s="9" t="inlineStr">
+      <c r="T2" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U2" s="9" t="inlineStr">
+      <c r="U2" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="V2" s="9" t="inlineStr">
+      <c r="V2" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="W2" s="10" t="inlineStr">
+      <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -771,28 +770,30 @@
       <c r="O3" t="n">
         <v>54216</v>
       </c>
-      <c r="P3" s="6" t="inlineStr"/>
-      <c r="Q3" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R3" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S3" s="8" t="inlineStr">
+      <c r="P3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T3" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U3" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V3" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W3" s="10" t="inlineStr">
+      <c r="T3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W3" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -851,30 +852,32 @@
       <c r="O4" t="n">
         <v>51255</v>
       </c>
-      <c r="P4" s="6" t="inlineStr"/>
-      <c r="Q4" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R4" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S4" s="8" t="inlineStr">
+      <c r="P4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T4" s="9" t="inlineStr">
+      <c r="T4" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U4" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V4" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W4" s="10" t="inlineStr">
+      <c r="U4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W4" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -933,32 +936,34 @@
       <c r="O5" t="n">
         <v>50519</v>
       </c>
-      <c r="P5" s="6" t="inlineStr"/>
-      <c r="Q5" s="7" t="inlineStr">
+      <c r="P5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q5" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R5" s="7" t="inlineStr">
+      <c r="R5" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S5" s="8" t="inlineStr">
+      <c r="S5" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T5" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U5" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V5" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W5" s="10" t="inlineStr">
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W5" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1017,30 +1022,32 @@
       <c r="O6" t="n">
         <v>50463</v>
       </c>
-      <c r="P6" s="6" t="inlineStr"/>
-      <c r="Q6" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="7" t="inlineStr">
+      <c r="P6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S6" s="8" t="inlineStr">
+      <c r="S6" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T6" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U6" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V6" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W6" s="10" t="inlineStr">
+      <c r="T6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W6" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1099,32 +1106,34 @@
       <c r="O7" t="n">
         <v>48555</v>
       </c>
-      <c r="P7" s="6" t="inlineStr"/>
-      <c r="Q7" s="7" t="inlineStr">
+      <c r="P7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q7" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R7" s="7" t="inlineStr">
+      <c r="R7" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S7" s="8" t="inlineStr">
+      <c r="S7" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T7" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U7" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V7" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W7" s="10" t="inlineStr">
+      <c r="T7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W7" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1183,30 +1192,32 @@
       <c r="O8" t="n">
         <v>49170</v>
       </c>
-      <c r="P8" s="6" t="inlineStr"/>
-      <c r="Q8" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S8" s="11" t="inlineStr">
+      <c r="P8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T8" s="9" t="inlineStr">
+      <c r="T8" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U8" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V8" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W8" s="10" t="inlineStr">
+      <c r="U8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W8" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1261,30 +1272,32 @@
       <c r="O9" t="n">
         <v>47760</v>
       </c>
-      <c r="P9" s="6" t="inlineStr"/>
-      <c r="Q9" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R9" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S9" s="11" t="inlineStr">
+      <c r="P9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T9" s="9" t="inlineStr">
+      <c r="T9" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U9" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V9" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W9" s="10" t="inlineStr">
+      <c r="U9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W9" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1339,32 +1352,34 @@
       <c r="O10" t="n">
         <v>48786</v>
       </c>
-      <c r="P10" s="6" t="inlineStr"/>
-      <c r="Q10" s="7" t="inlineStr">
+      <c r="P10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q10" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R10" s="7" t="inlineStr">
+      <c r="R10" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S10" s="8" t="inlineStr">
+      <c r="S10" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T10" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U10" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V10" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W10" s="10" t="inlineStr">
+      <c r="T10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W10" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1423,32 +1438,34 @@
       <c r="O11" t="n">
         <v>48386</v>
       </c>
-      <c r="P11" s="6" t="inlineStr"/>
-      <c r="Q11" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R11" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S11" s="11" t="inlineStr">
+      <c r="P11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T11" s="9" t="inlineStr">
+      <c r="T11" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U11" s="9" t="inlineStr">
+      <c r="U11" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V11" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W11" s="10" t="inlineStr">
+      <c r="V11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W11" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1507,28 +1524,30 @@
       <c r="O12" t="n">
         <v>49014</v>
       </c>
-      <c r="P12" s="6" t="inlineStr"/>
-      <c r="Q12" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R12" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S12" s="11" t="inlineStr">
+      <c r="P12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T12" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U12" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V12" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W12" s="10" t="inlineStr">
+      <c r="T12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W12" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1583,30 +1602,32 @@
       <c r="O13" t="n">
         <v>49271</v>
       </c>
-      <c r="P13" s="6" t="inlineStr"/>
-      <c r="Q13" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R13" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S13" s="8" t="inlineStr">
+      <c r="P13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T13" s="9" t="inlineStr">
+      <c r="T13" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U13" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V13" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W13" s="10" t="inlineStr">
+      <c r="U13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W13" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1665,32 +1686,34 @@
       <c r="O14" t="n">
         <v>49406</v>
       </c>
-      <c r="P14" s="6" t="inlineStr"/>
-      <c r="Q14" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R14" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S14" s="11" t="inlineStr">
+      <c r="P14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T14" s="9" t="inlineStr">
+      <c r="T14" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U14" s="9" t="inlineStr">
+      <c r="U14" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V14" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W14" s="10" t="inlineStr">
+      <c r="V14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W14" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1749,30 +1772,32 @@
       <c r="O15" t="n">
         <v>49626</v>
       </c>
-      <c r="P15" s="6" t="inlineStr"/>
-      <c r="Q15" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R15" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S15" s="11" t="inlineStr">
+      <c r="P15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T15" s="9" t="inlineStr">
+      <c r="T15" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U15" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V15" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W15" s="10" t="inlineStr">
+      <c r="U15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W15" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1827,30 +1852,32 @@
       <c r="O16" t="n">
         <v>50396</v>
       </c>
-      <c r="P16" s="6" t="inlineStr"/>
-      <c r="Q16" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R16" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="11" t="inlineStr">
+      <c r="P16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T16" s="9" t="inlineStr">
+      <c r="T16" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U16" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V16" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W16" s="10" t="inlineStr">
+      <c r="U16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W16" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1909,34 +1936,36 @@
       <c r="O17" t="n">
         <v>49974</v>
       </c>
-      <c r="P17" s="6" t="inlineStr"/>
-      <c r="Q17" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R17" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="11" t="inlineStr">
+      <c r="P17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T17" s="9" t="inlineStr">
+      <c r="T17" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U17" s="9" t="inlineStr">
+      <c r="U17" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="V17" s="9" t="inlineStr">
+      <c r="V17" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="W17" s="10" t="inlineStr">
+      <c r="W17" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1956,19 +1985,19 @@
         <v>49594</v>
       </c>
       <c r="D18" t="n">
-        <v>47850</v>
+        <v>46456</v>
       </c>
       <c r="E18" t="n">
-        <v>47945</v>
+        <v>47366</v>
       </c>
       <c r="F18" t="n">
-        <v>-760</v>
+        <v>-1339</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0156</v>
+        <v>-0.0275</v>
       </c>
       <c r="H18" t="n">
-        <v>1744</v>
+        <v>3138</v>
       </c>
       <c r="I18" t="n">
         <v>46561</v>
@@ -1991,30 +2020,36 @@
       <c r="O18" t="n">
         <v>52117</v>
       </c>
-      <c r="P18" s="6" t="inlineStr"/>
-      <c r="Q18" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R18" s="7" t="inlineStr">
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S18" s="8" t="inlineStr">
+      <c r="S18" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T18" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V18" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W18" s="10" t="inlineStr">
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W18" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>

--- a/three_gate/analysis/TX_weekly.xlsx
+++ b/three_gate/analysis/TX_weekly.xlsx
@@ -1988,13 +1988,13 @@
         <v>46456</v>
       </c>
       <c r="E18" t="n">
-        <v>47366</v>
+        <v>47242</v>
       </c>
       <c r="F18" t="n">
-        <v>-1339</v>
+        <v>-1463</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0275</v>
+        <v>-0.03</v>
       </c>
       <c r="H18" t="n">
         <v>3138</v>

--- a/three_gate/analysis/TX_weekly.xlsx
+++ b/three_gate/analysis/TX_weekly.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X18"/>
+  <dimension ref="A1:X19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2060,6 +2060,90 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>47269</v>
+      </c>
+      <c r="C19" t="n">
+        <v>47380</v>
+      </c>
+      <c r="D19" t="n">
+        <v>46107</v>
+      </c>
+      <c r="E19" t="n">
+        <v>46140</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-1102</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>-0.0233</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1273</v>
+      </c>
+      <c r="I19" t="n">
+        <v>43318</v>
+      </c>
+      <c r="J19" t="n">
+        <v>43712.5</v>
+      </c>
+      <c r="K19" t="n">
+        <v>45673</v>
+      </c>
+      <c r="L19" t="n">
+        <v>47633.5</v>
+      </c>
+      <c r="M19" t="n">
+        <v>48811</v>
+      </c>
+      <c r="N19" t="n">
+        <v>49988.5</v>
+      </c>
+      <c r="O19" t="n">
+        <v>52732</v>
+      </c>
+      <c r="P19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W19" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/TX_weekly.xlsx
+++ b/three_gate/analysis/TX_weekly.xlsx
@@ -2067,25 +2067,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>47269</v>
+        <v>46627</v>
       </c>
       <c r="C19" t="n">
-        <v>47380</v>
+        <v>47033</v>
       </c>
       <c r="D19" t="n">
-        <v>46107</v>
+        <v>46390</v>
       </c>
       <c r="E19" t="n">
-        <v>46140</v>
+        <v>46691</v>
       </c>
       <c r="F19" t="n">
-        <v>-1102</v>
+        <v>-551</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0233</v>
+        <v>-0.0117</v>
       </c>
       <c r="H19" t="n">
-        <v>1273</v>
+        <v>643</v>
       </c>
       <c r="I19" t="n">
         <v>43318</v>
@@ -2114,14 +2114,12 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R19" s="6" t="n">
+        <v/>
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T19" s="8" t="n">

--- a/three_gate/analysis/TX_weekly.xlsx
+++ b/three_gate/analysis/TX_weekly.xlsx
@@ -2070,22 +2070,22 @@
         <v>46627</v>
       </c>
       <c r="C19" t="n">
-        <v>47033</v>
+        <v>47098</v>
       </c>
       <c r="D19" t="n">
-        <v>46390</v>
+        <v>46136</v>
       </c>
       <c r="E19" t="n">
-        <v>46691</v>
+        <v>46975</v>
       </c>
       <c r="F19" t="n">
-        <v>-551</v>
+        <v>-267</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0117</v>
+        <v>-0.0057</v>
       </c>
       <c r="H19" t="n">
-        <v>643</v>
+        <v>962</v>
       </c>
       <c r="I19" t="n">
         <v>43318</v>

--- a/three_gate/analysis/TX_weekly.xlsx
+++ b/three_gate/analysis/TX_weekly.xlsx
@@ -2070,22 +2070,22 @@
         <v>46627</v>
       </c>
       <c r="C19" t="n">
-        <v>47098</v>
+        <v>47555</v>
       </c>
       <c r="D19" t="n">
         <v>46136</v>
       </c>
       <c r="E19" t="n">
-        <v>46975</v>
+        <v>47482</v>
       </c>
       <c r="F19" t="n">
-        <v>-267</v>
+        <v>240</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0057</v>
+        <v>0.0051</v>
       </c>
       <c r="H19" t="n">
-        <v>962</v>
+        <v>1419</v>
       </c>
       <c r="I19" t="n">
         <v>43318</v>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/TX_weekly.xlsx
+++ b/three_gate/analysis/TX_weekly.xlsx
@@ -2073,19 +2073,19 @@
         <v>47555</v>
       </c>
       <c r="D19" t="n">
-        <v>46136</v>
+        <v>45523</v>
       </c>
       <c r="E19" t="n">
-        <v>47482</v>
+        <v>45654</v>
       </c>
       <c r="F19" t="n">
-        <v>240</v>
+        <v>-1588</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0051</v>
+        <v>-0.0336</v>
       </c>
       <c r="H19" t="n">
-        <v>1419</v>
+        <v>2032</v>
       </c>
       <c r="I19" t="n">
         <v>43318</v>
@@ -2114,12 +2114,14 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="n">
-        <v/>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T19" s="8" t="n">
@@ -2138,7 +2140,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/TX_weekly.xlsx
+++ b/three_gate/analysis/TX_weekly.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X19"/>
+  <dimension ref="A1:X20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2144,6 +2144,88 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>46270</v>
+      </c>
+      <c r="C20" t="n">
+        <v>46399</v>
+      </c>
+      <c r="D20" t="n">
+        <v>45523</v>
+      </c>
+      <c r="E20" t="n">
+        <v>45654</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>876</v>
+      </c>
+      <c r="I20" t="n">
+        <v>43491</v>
+      </c>
+      <c r="J20" t="n">
+        <v>43179.5</v>
+      </c>
+      <c r="K20" t="n">
+        <v>44638</v>
+      </c>
+      <c r="L20" t="n">
+        <v>46096.5</v>
+      </c>
+      <c r="M20" t="n">
+        <v>46670</v>
+      </c>
+      <c r="N20" t="n">
+        <v>47243.5</v>
+      </c>
+      <c r="O20" t="n">
+        <v>49587</v>
+      </c>
+      <c r="P20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W20" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/TX_weekly.xlsx
+++ b/three_gate/analysis/TX_weekly.xlsx
@@ -2151,25 +2151,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>46270</v>
+        <v>46505</v>
       </c>
       <c r="C20" t="n">
-        <v>46399</v>
+        <v>47000</v>
       </c>
       <c r="D20" t="n">
-        <v>45523</v>
+        <v>46006</v>
       </c>
       <c r="E20" t="n">
-        <v>45654</v>
+        <v>46880</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>1226</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0</v>
+        <v>0.0269</v>
       </c>
       <c r="H20" t="n">
-        <v>876</v>
+        <v>994</v>
       </c>
       <c r="I20" t="n">
         <v>43491</v>
@@ -2201,13 +2201,15 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U20" s="8" t="n">
         <v/>

--- a/three_gate/analysis/TX_weekly.xlsx
+++ b/three_gate/analysis/TX_weekly.xlsx
@@ -2154,22 +2154,22 @@
         <v>46505</v>
       </c>
       <c r="C20" t="n">
-        <v>47000</v>
+        <v>47607</v>
       </c>
       <c r="D20" t="n">
         <v>46006</v>
       </c>
       <c r="E20" t="n">
-        <v>46880</v>
+        <v>47121</v>
       </c>
       <c r="F20" t="n">
-        <v>1226</v>
+        <v>1467</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0269</v>
+        <v>0.0321</v>
       </c>
       <c r="H20" t="n">
-        <v>994</v>
+        <v>1601</v>
       </c>
       <c r="I20" t="n">
         <v>43491</v>
@@ -2208,12 +2208,14 @@
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U20" s="8" t="n">
-        <v/>
-      </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
@@ -2222,11 +2224,7 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/TX_weekly.xlsx
+++ b/three_gate/analysis/TX_weekly.xlsx
@@ -2157,19 +2157,19 @@
         <v>47607</v>
       </c>
       <c r="D20" t="n">
-        <v>46006</v>
+        <v>45850</v>
       </c>
       <c r="E20" t="n">
-        <v>47121</v>
+        <v>45926</v>
       </c>
       <c r="F20" t="n">
-        <v>1467</v>
+        <v>272</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0321</v>
+        <v>0.006</v>
       </c>
       <c r="H20" t="n">
-        <v>1601</v>
+        <v>1757</v>
       </c>
       <c r="I20" t="n">
         <v>43491</v>
@@ -2201,9 +2201,9 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="U20" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="V20" s="8" t="n">

--- a/three_gate/analysis/TX_weekly.xlsx
+++ b/three_gate/analysis/TX_weekly.xlsx
@@ -2157,19 +2157,19 @@
         <v>47607</v>
       </c>
       <c r="D20" t="n">
-        <v>45850</v>
+        <v>44908</v>
       </c>
       <c r="E20" t="n">
-        <v>45926</v>
+        <v>45301</v>
       </c>
       <c r="F20" t="n">
-        <v>272</v>
+        <v>-353</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.006</v>
+        <v>-0.0077</v>
       </c>
       <c r="H20" t="n">
-        <v>1757</v>
+        <v>2699</v>
       </c>
       <c r="I20" t="n">
         <v>43491</v>
@@ -2198,12 +2198,14 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="n">
-        <v/>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
@@ -2224,7 +2226,11 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
